--- a/ig/DM-DECEMBRE-2025/ValueSet-JDV-J226-ModaliteAccueil-ROR.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-JDV-J226-ModaliteAccueil-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="83">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250828120000</t>
+    <t>20251222120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-28T12:00:00+01:00</t>
+    <t>2025-12-22T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -241,6 +241,18 @@
   </si>
   <si>
     <t>Autodialyse assistée</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Relayage courte durée (quelques heures par jour)</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Relayage longue durée (sur plusieurs jours)</t>
   </si>
   <si>
     <t/>
@@ -511,7 +523,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -723,15 +735,31 @@
         <v>76</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
